--- a/sources/julia_step6b.xlsx
+++ b/sources/julia_step6b.xlsx
@@ -874,6 +874,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -921,6 +926,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -968,6 +978,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -1013,6 +1028,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -5983,6 +6003,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -6015,6 +6040,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -6045,6 +6075,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">

--- a/sources/julia_step6b.xlsx
+++ b/sources/julia_step6b.xlsx
@@ -4189,6 +4189,11 @@
           <t>– 1+2</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>– Back Push</t>
